--- a/public/exports-60-250/29189803.xlsx
+++ b/public/exports-60-250/29189803.xlsx
@@ -8141,40 +8141,40 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Strynøvej 8</t>
+          <t xml:space="preserve">Novrupvej 47</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t xml:space="preserve">5119870</t>
+          <t xml:space="preserve">5746884</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J109">
-        <v>172</v>
+        <v>201</v>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t xml:space="preserve">100102885</t>
+          <t xml:space="preserve">200014518</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Martin Jessen Rådg. ing. FRI</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t xml:space="preserve">2018-11-03</t>
+          <t xml:space="preserve">2019-06-03</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8231,11 +8231,11 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J110">
-        <v>201</v>
+        <v>73</v>
       </c>
       <c r="K110" t="inlineStr">
         <is>
@@ -8291,40 +8291,40 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t xml:space="preserve">Novrupvej 47</t>
+          <t xml:space="preserve">Skolevej 35A</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6731</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t xml:space="preserve">5746884</t>
+          <t xml:space="preserve">5133594</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J111">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t xml:space="preserve">200014518</t>
+          <t xml:space="preserve">200015289</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-03</t>
+          <t xml:space="preserve">2019-06-18</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8366,7 +8366,7 @@
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 35A</t>
+          <t xml:space="preserve">Skolevej 35D</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J112">
@@ -8441,22 +8441,22 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 35D</t>
+          <t xml:space="preserve">Højvangshaven 12</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t xml:space="preserve">6731</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">5133594</t>
+          <t xml:space="preserve">7497842</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J113">
@@ -8464,17 +8464,17 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t xml:space="preserve">200015289</t>
+          <t xml:space="preserve">200019061</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-06-18</t>
+          <t xml:space="preserve">2019-08-21</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højvangshaven 12</t>
+          <t xml:space="preserve">Højvangshaven 6</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
@@ -8531,7 +8531,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J114">
@@ -8591,7 +8591,7 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Højvangshaven 6</t>
+          <t xml:space="preserve">Ribegade 149</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -8601,20 +8601,20 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">7497842</t>
+          <t xml:space="preserve">7976965</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J115">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t xml:space="preserve">200019061</t>
+          <t xml:space="preserve">200021276</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-08-21</t>
+          <t xml:space="preserve">2019-09-29</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8666,7 +8666,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ribegade 149</t>
+          <t xml:space="preserve">Bjarkesgade 14</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -8676,7 +8676,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">7976965</t>
+          <t xml:space="preserve">5734841</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -8685,21 +8685,21 @@
         </is>
       </c>
       <c r="J116">
-        <v>203</v>
+        <v>147</v>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021276</t>
+          <t xml:space="preserve">200021450</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Vejle)</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-29</t>
+          <t xml:space="preserve">2019-09-30</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8741,35 +8741,35 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bjarkesgade 14</t>
+          <t xml:space="preserve">Gabelsvej 8</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">5734841</t>
+          <t xml:space="preserve">9671465</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J117">
-        <v>147</v>
+        <v>64</v>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021450</t>
+          <t xml:space="preserve">200021461</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gabelsvej 8</t>
+          <t xml:space="preserve">Idræts Alle 12A</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -8831,11 +8831,11 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">16</t>
         </is>
       </c>
       <c r="J118">
-        <v>64</v>
+        <v>232</v>
       </c>
       <c r="K118" t="inlineStr">
         <is>
@@ -8891,35 +8891,35 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Idræts Alle 12A</t>
+          <t xml:space="preserve">Jernbanegade 47</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t xml:space="preserve">9671465</t>
+          <t xml:space="preserve">8038805</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t xml:space="preserve">16</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J119">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021461</t>
+          <t xml:space="preserve">200021480</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M119" t="inlineStr">
@@ -8966,17 +8966,17 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jernbanegade 47</t>
+          <t xml:space="preserve">Landlystvej 7A</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">8038805</t>
+          <t xml:space="preserve">5108524</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -8985,16 +8985,16 @@
         </is>
       </c>
       <c r="J120">
-        <v>220</v>
+        <v>201</v>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021480</t>
+          <t xml:space="preserve">200021574</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
         </is>
       </c>
       <c r="M120" t="inlineStr">
@@ -9041,17 +9041,17 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Landlystvej 7A</t>
+          <t xml:space="preserve">Neptunvej 29</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t xml:space="preserve">5108524</t>
+          <t xml:space="preserve">5121097</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -9060,16 +9060,16 @@
         </is>
       </c>
       <c r="J121">
-        <v>201</v>
+        <v>239</v>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021574</t>
+          <t xml:space="preserve">200021474</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Vejle)</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M121" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t xml:space="preserve">Neptunvej 29</t>
+          <t xml:space="preserve">Ålykken 71</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -9126,7 +9126,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t xml:space="preserve">5121097</t>
+          <t xml:space="preserve">5119276</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -9135,11 +9135,11 @@
         </is>
       </c>
       <c r="J122">
-        <v>239</v>
+        <v>180</v>
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t xml:space="preserve">200021474</t>
+          <t xml:space="preserve">100136130</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
@@ -9191,7 +9191,7 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ålykken 71</t>
+          <t xml:space="preserve">Gravlundvej 1</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
@@ -9201,20 +9201,20 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t xml:space="preserve">5119276</t>
+          <t xml:space="preserve">9061698</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J123">
-        <v>180</v>
+        <v>76</v>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t xml:space="preserve">100136130</t>
+          <t xml:space="preserve">200025356</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-09-30</t>
+          <t xml:space="preserve">2019-12-11</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9266,40 +9266,40 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gravlundvej 1</t>
+          <t xml:space="preserve">Vestre Lufthavnsvej 27</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t xml:space="preserve">9061698</t>
+          <t xml:space="preserve">8865861</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J124">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t xml:space="preserve">200025356</t>
+          <t xml:space="preserve">100147076</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Rådgivende ingeniørfirma FRI Poul Skærbæk</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019-12-11</t>
+          <t xml:space="preserve">2020-01-20</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9341,40 +9341,40 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vestre Lufthavnsvej 27</t>
+          <t xml:space="preserve">Grønningen 2G</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t xml:space="preserve">8865861</t>
+          <t xml:space="preserve">5046168</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J125">
-        <v>109</v>
+        <v>186</v>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t xml:space="preserve">100147076</t>
+          <t xml:space="preserve">200028555</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rådgivende ingeniørfirma FRI Poul Skærbæk</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-01-20</t>
+          <t xml:space="preserve">2020-02-26</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9416,30 +9416,30 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 2G</t>
+          <t xml:space="preserve">Storegade 307</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t xml:space="preserve">5046168</t>
+          <t xml:space="preserve">9433154</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J126">
-        <v>186</v>
+        <v>164</v>
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t xml:space="preserve">200028555</t>
+          <t xml:space="preserve">100151920</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
@@ -9449,7 +9449,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-02-26</t>
+          <t xml:space="preserve">2020-03-12</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9491,17 +9491,17 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 307</t>
+          <t xml:space="preserve">Sønderhedevej 23</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t xml:space="preserve">9433154</t>
+          <t xml:space="preserve">9222849</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -9510,11 +9510,11 @@
         </is>
       </c>
       <c r="J127">
-        <v>164</v>
+        <v>174</v>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t xml:space="preserve">100151920</t>
+          <t xml:space="preserve">100151931</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -9566,17 +9566,17 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sønderhedevej 23</t>
+          <t xml:space="preserve">Søndre Novrupvej 11</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t xml:space="preserve">9222849</t>
+          <t xml:space="preserve">9475419</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -9585,11 +9585,11 @@
         </is>
       </c>
       <c r="J128">
-        <v>174</v>
+        <v>119</v>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t xml:space="preserve">100151931</t>
+          <t xml:space="preserve">100151921</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -9641,17 +9641,17 @@
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Søndre Novrupvej 11</t>
+          <t xml:space="preserve">Tarp Byvej 6</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t xml:space="preserve">9475419</t>
+          <t xml:space="preserve">5111046</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
@@ -9660,11 +9660,11 @@
         </is>
       </c>
       <c r="J129">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t xml:space="preserve">100151921</t>
+          <t xml:space="preserve">100151928</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -9716,40 +9716,40 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarp Byvej 6</t>
+          <t xml:space="preserve">Solgårdsvej 6</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">5111046</t>
+          <t xml:space="preserve">8395247</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
       <c r="J130">
-        <v>81</v>
+        <v>176</v>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t xml:space="preserve">100151928</t>
+          <t xml:space="preserve">200029500</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
         </is>
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-12</t>
+          <t xml:space="preserve">2020-03-19</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9791,30 +9791,30 @@
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Solgårdsvej 6</t>
+          <t xml:space="preserve">Skovkanten 12</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t xml:space="preserve">8395247</t>
+          <t xml:space="preserve">5738607</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t xml:space="preserve">10</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J131">
-        <v>176</v>
+        <v>232</v>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t xml:space="preserve">200029500</t>
+          <t xml:space="preserve">200030925</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -9824,7 +9824,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-03-19</t>
+          <t xml:space="preserve">2020-04-29</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9866,7 +9866,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 12</t>
+          <t xml:space="preserve">Skovkanten 14</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
@@ -9876,7 +9876,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738607</t>
+          <t xml:space="preserve">5738606</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030925</t>
+          <t xml:space="preserve">200030924</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -9941,7 +9941,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 14</t>
+          <t xml:space="preserve">Skovkanten 16</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738606</t>
+          <t xml:space="preserve">5738605</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -9964,7 +9964,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030924</t>
+          <t xml:space="preserve">200030920</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 16</t>
+          <t xml:space="preserve">Skovkanten 18</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738605</t>
+          <t xml:space="preserve">5738604</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -10035,11 +10035,11 @@
         </is>
       </c>
       <c r="J134">
-        <v>232</v>
+        <v>244</v>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030920</t>
+          <t xml:space="preserve">200030923</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -10091,7 +10091,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 18</t>
+          <t xml:space="preserve">Skovkanten 22</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -10101,7 +10101,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738604</t>
+          <t xml:space="preserve">5738603</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030923</t>
+          <t xml:space="preserve">200030922</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 22</t>
+          <t xml:space="preserve">Skovkanten 4</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738603</t>
+          <t xml:space="preserve">5738609</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -10189,7 +10189,7 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030922</t>
+          <t xml:space="preserve">200030921</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 4</t>
+          <t xml:space="preserve">Skovkanten 8</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -10251,7 +10251,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738609</t>
+          <t xml:space="preserve">5738608</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -10264,7 +10264,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030921</t>
+          <t xml:space="preserve">200030926</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -10316,17 +10316,17 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skovkanten 8</t>
+          <t xml:space="preserve">Veldtoftevej 12</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738608</t>
+          <t xml:space="preserve">9475433</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -10335,21 +10335,21 @@
         </is>
       </c>
       <c r="J138">
-        <v>244</v>
+        <v>157</v>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t xml:space="preserve">200030926</t>
+          <t xml:space="preserve">100158184</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Vejle)</t>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
         </is>
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-04-29</t>
+          <t xml:space="preserve">2020-05-04</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10391,7 +10391,7 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t xml:space="preserve">Veldtoftevej 12</t>
+          <t xml:space="preserve">Østre Kjersingvej 21</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t xml:space="preserve">9475433</t>
+          <t xml:space="preserve">8388139</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -10410,11 +10410,11 @@
         </is>
       </c>
       <c r="J139">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t xml:space="preserve">100158184</t>
+          <t xml:space="preserve">100158181</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -10466,17 +10466,17 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t xml:space="preserve">Østre Kjersingvej 21</t>
+          <t xml:space="preserve">Stormgade 258</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388139</t>
+          <t xml:space="preserve">8388154</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -10485,11 +10485,11 @@
         </is>
       </c>
       <c r="J140">
-        <v>155</v>
+        <v>210</v>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t xml:space="preserve">100158181</t>
+          <t xml:space="preserve">100158360</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -10499,7 +10499,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-04</t>
+          <t xml:space="preserve">2020-05-05</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10541,17 +10541,17 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stormgade 258</t>
+          <t xml:space="preserve">Tradsborgvej 16</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6731</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388154</t>
+          <t xml:space="preserve">9243321</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -10560,11 +10560,11 @@
         </is>
       </c>
       <c r="J141">
-        <v>210</v>
+        <v>121</v>
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t xml:space="preserve">100158360</t>
+          <t xml:space="preserve">100158357</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -10616,17 +10616,17 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tradsborgvej 16</t>
+          <t xml:space="preserve">Baggesens Alle 10</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t xml:space="preserve">6731</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t xml:space="preserve">9243321</t>
+          <t xml:space="preserve">5735054</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -10635,11 +10635,11 @@
         </is>
       </c>
       <c r="J142">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t xml:space="preserve">100158357</t>
+          <t xml:space="preserve">200032449</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -10649,7 +10649,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-05-05</t>
+          <t xml:space="preserve">2020-06-10</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10691,17 +10691,17 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Baggesens Alle 10</t>
+          <t xml:space="preserve">Ølufvad Hovedvej 83</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t xml:space="preserve">5735054</t>
+          <t xml:space="preserve">5123806</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -10710,16 +10710,16 @@
         </is>
       </c>
       <c r="J143">
-        <v>155</v>
+        <v>71</v>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032449</t>
+          <t xml:space="preserve">200032424</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M143" t="inlineStr">
@@ -10766,40 +10766,40 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ølufvad Hovedvej 83</t>
+          <t xml:space="preserve">Storegade 307</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t xml:space="preserve">5123806</t>
+          <t xml:space="preserve">9433154</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J144">
-        <v>71</v>
+        <v>200</v>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032424</t>
+          <t xml:space="preserve">200032892</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
         </is>
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-10</t>
+          <t xml:space="preserve">2020-06-23</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10841,40 +10841,40 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storegade 307</t>
+          <t xml:space="preserve">Kjærgårdsvej 9D</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">9433154</t>
+          <t xml:space="preserve">736932, 5052565</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J145">
-        <v>200</v>
+        <v>73</v>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t xml:space="preserve">200032892</t>
+          <t xml:space="preserve">200033093</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-23</t>
+          <t xml:space="preserve">2020-06-28</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10916,40 +10916,40 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kjærgårdsvej 9D</t>
+          <t xml:space="preserve">Grønnegårdsvej 8</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t xml:space="preserve">736932, 5052565</t>
+          <t xml:space="preserve">5745295</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J146">
-        <v>73</v>
+        <v>221</v>
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t xml:space="preserve">200033093</t>
+          <t xml:space="preserve">200035324</t>
         </is>
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-06-28</t>
+          <t xml:space="preserve">2020-08-16</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10991,30 +10991,30 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 8</t>
+          <t xml:space="preserve">Grådybparken 19</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t xml:space="preserve">5745295</t>
+          <t xml:space="preserve">5738772</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J147">
-        <v>221</v>
+        <v>129</v>
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t xml:space="preserve">200035324</t>
+          <t xml:space="preserve">200039948</t>
         </is>
       </c>
       <c r="L147" t="inlineStr">
@@ -11024,7 +11024,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-08-16</t>
+          <t xml:space="preserve">2020-10-28</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -11066,17 +11066,17 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grådybparken 19</t>
+          <t xml:space="preserve">Tarp Byvej 85</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">5738772</t>
+          <t xml:space="preserve">10036827</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -11085,11 +11085,11 @@
         </is>
       </c>
       <c r="J148">
-        <v>129</v>
+        <v>162</v>
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039948</t>
+          <t xml:space="preserve">200039947</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -11141,30 +11141,30 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarp Byvej 85</t>
+          <t xml:space="preserve">Grønningen 3B</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t xml:space="preserve">10036827</t>
+          <t xml:space="preserve">5046407</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J149">
-        <v>162</v>
+        <v>221</v>
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t xml:space="preserve">200039947</t>
+          <t xml:space="preserve">200040064</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
@@ -11174,7 +11174,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-28</t>
+          <t xml:space="preserve">2020-10-29</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -11216,40 +11216,40 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønningen 3B</t>
+          <t xml:space="preserve">Birkekrattet 4</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t xml:space="preserve">5046407</t>
+          <t xml:space="preserve">8725263</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J150">
-        <v>221</v>
+        <v>110</v>
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t xml:space="preserve">200040064</t>
+          <t xml:space="preserve">200052050</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t xml:space="preserve">Brix &amp; Kamp A/S</t>
+          <t xml:space="preserve">COWI A/S (Vejle)</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020-10-29</t>
+          <t xml:space="preserve">2021-08-17</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11291,40 +11291,40 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t xml:space="preserve">Birkekrattet 4</t>
+          <t xml:space="preserve">Gabelsvej 8</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t xml:space="preserve">8725263</t>
+          <t xml:space="preserve">9671465</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J151">
-        <v>110</v>
+        <v>162</v>
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t xml:space="preserve">200052050</t>
+          <t xml:space="preserve">200059087</t>
         </is>
       </c>
       <c r="L151" t="inlineStr">
         <is>
-          <t xml:space="preserve">COWI A/S (Vejle)</t>
+          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
         </is>
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t xml:space="preserve">2021-08-17</t>
+          <t xml:space="preserve">2022-04-24</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11366,40 +11366,40 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gabelsvej 8</t>
+          <t xml:space="preserve">Skads Byvej 93</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">9671465</t>
+          <t xml:space="preserve">7912300</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J152">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t xml:space="preserve">200059087</t>
+          <t xml:space="preserve">100266185</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t xml:space="preserve">BRIX &amp; KAMP A/S</t>
+          <t xml:space="preserve">R arkitekter, Esbjerg</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-24</t>
+          <t xml:space="preserve">2022-04-26</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11441,40 +11441,40 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skads Byvej 93</t>
+          <t xml:space="preserve">Mukkerten 14</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">7912300</t>
+          <t xml:space="preserve">8042751</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J153">
-        <v>166</v>
+        <v>94</v>
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t xml:space="preserve">100266185</t>
+          <t xml:space="preserve">311051467</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t xml:space="preserve">R arkitekter, Esbjerg</t>
+          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t xml:space="preserve">2022-04-26</t>
+          <t xml:space="preserve">2024-04-30</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11516,40 +11516,40 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mukkerten 14</t>
+          <t xml:space="preserve">Skads Byvej 102</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">8042751</t>
+          <t xml:space="preserve">5748022</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J154">
-        <v>94</v>
+        <v>247</v>
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t xml:space="preserve">311051467</t>
+          <t xml:space="preserve">311087026</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek Center Sydvestjylland</t>
+          <t xml:space="preserve">R arkitekter, Esbjerg</t>
         </is>
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-04-30</t>
+          <t xml:space="preserve">2024-12-08</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11591,17 +11591,17 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skads Byvej 102</t>
+          <t xml:space="preserve">Ole Rømers Vej 50</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">5748022</t>
+          <t xml:space="preserve">7656815</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -11610,31 +11610,31 @@
         </is>
       </c>
       <c r="J155">
-        <v>247</v>
+        <v>66</v>
       </c>
       <c r="K155" t="inlineStr">
         <is>
-          <t xml:space="preserve">311087026</t>
+          <t xml:space="preserve">311359415</t>
         </is>
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t xml:space="preserve">R arkitekter, Esbjerg</t>
+          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t xml:space="preserve">2024-12-08</t>
+          <t xml:space="preserve">2029-02-13</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Udløbet</t>
+          <t xml:space="preserve">Gyldigt</t>
         </is>
       </c>
       <c r="O155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ja</t>
+          <t xml:space="preserve">Nej</t>
         </is>
       </c>
     </row>
@@ -11666,17 +11666,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ole Rømers Vej 50</t>
+          <t xml:space="preserve">Måde Kirkevej 35</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t xml:space="preserve">7656815</t>
+          <t xml:space="preserve">8948776</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -11685,21 +11685,21 @@
         </is>
       </c>
       <c r="J156">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="K156" t="inlineStr">
         <is>
-          <t xml:space="preserve">311359415</t>
+          <t xml:space="preserve">311359647</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energi- og Bygningsrådgivning A/S</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-13</t>
+          <t xml:space="preserve">2029-02-14</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11741,40 +11741,40 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Måde Kirkevej 35</t>
+          <t xml:space="preserve">Bygaden 43</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">8948776</t>
+          <t xml:space="preserve">5054539</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J157">
-        <v>94</v>
+        <v>196</v>
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t xml:space="preserve">311359647</t>
+          <t xml:space="preserve">311442081</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">BYGTEST ApS</t>
         </is>
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t xml:space="preserve">2029-02-14</t>
+          <t xml:space="preserve">2030-06-08</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11816,17 +11816,17 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bygaden 43</t>
+          <t xml:space="preserve">Ringen 61E</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t xml:space="preserve">5054539</t>
+          <t xml:space="preserve">8388410</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -11835,21 +11835,21 @@
         </is>
       </c>
       <c r="J158">
-        <v>196</v>
+        <v>141</v>
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t xml:space="preserve">311442101</t>
+          <t xml:space="preserve">311567887</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t xml:space="preserve">BYGTEST ApS</t>
+          <t xml:space="preserve">VITA Ingeniører</t>
         </is>
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t xml:space="preserve">2030-06-08</t>
+          <t xml:space="preserve">2031-12-14</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringen 61E</t>
+          <t xml:space="preserve">Ringen 61F</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -11906,11 +11906,11 @@
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J159">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="K159" t="inlineStr">
         <is>
@@ -11966,17 +11966,17 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ringen 61F</t>
+          <t xml:space="preserve">Skolevej 32</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6731</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388410</t>
+          <t xml:space="preserve">5133969</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -11985,11 +11985,11 @@
         </is>
       </c>
       <c r="J160">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567887</t>
+          <t xml:space="preserve">311567884</t>
         </is>
       </c>
       <c r="L160" t="inlineStr">
@@ -12041,30 +12041,30 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolevej 32</t>
+          <t xml:space="preserve">Skrænten 120</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t xml:space="preserve">6731</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t xml:space="preserve">5133969</t>
+          <t xml:space="preserve">5746415</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J161">
-        <v>153</v>
+        <v>104</v>
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567884</t>
+          <t xml:space="preserve">311567883</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
@@ -12116,30 +12116,30 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skrænten 120</t>
+          <t xml:space="preserve">Kongeåvej 17</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6771</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t xml:space="preserve">5746415</t>
+          <t xml:space="preserve">5053434</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J162">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t xml:space="preserve">311567883</t>
+          <t xml:space="preserve">311582274</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
@@ -12149,7 +12149,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t xml:space="preserve">2031-12-14</t>
+          <t xml:space="preserve">2032-03-03</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -12206,11 +12206,11 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J163">
-        <v>246</v>
+        <v>184</v>
       </c>
       <c r="K163" t="inlineStr">
         <is>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongeåvej 17</t>
+          <t xml:space="preserve">Kongeåvej 17A</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
@@ -12281,15 +12281,15 @@
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J164">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582274</t>
+          <t xml:space="preserve">311582276</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -12336,35 +12336,35 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t xml:space="preserve">561</t>
+          <t xml:space="preserve">540</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kongeåvej 17A</t>
+          <t xml:space="preserve">Rendbjergvej 12</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t xml:space="preserve">6771</t>
+          <t xml:space="preserve">6320</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5053434</t>
+          <t xml:space="preserve">5283241</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J165">
-        <v>186</v>
+        <v>210</v>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582276</t>
+          <t xml:space="preserve">311582270</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -12431,15 +12431,15 @@
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J166">
-        <v>210</v>
+        <v>152</v>
       </c>
       <c r="K166" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582270</t>
+          <t xml:space="preserve">311582271</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
@@ -12486,35 +12486,35 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t xml:space="preserve">540</t>
+          <t xml:space="preserve">561</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rendbjergvej 12</t>
+          <t xml:space="preserve">Bakkevej 2</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t xml:space="preserve">6320</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5283241</t>
+          <t xml:space="preserve">5046638</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J167">
-        <v>152</v>
+        <v>194</v>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t xml:space="preserve">311582271</t>
+          <t xml:space="preserve">311594111</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-03-03</t>
+          <t xml:space="preserve">2032-04-21</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12566,30 +12566,30 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 2</t>
+          <t xml:space="preserve">Haulundvej 3</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t xml:space="preserve">5046638</t>
+          <t xml:space="preserve">5752935</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J168">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="K168" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594111</t>
+          <t xml:space="preserve">311594113</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
@@ -12656,15 +12656,15 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J169">
-        <v>138</v>
+        <v>90</v>
       </c>
       <c r="K169" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594113</t>
+          <t xml:space="preserve">311594112</t>
         </is>
       </c>
       <c r="L169" t="inlineStr">
@@ -12716,30 +12716,30 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t xml:space="preserve">Haulundvej 3</t>
+          <t xml:space="preserve">Skolebakken 166</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t xml:space="preserve">5752935</t>
+          <t xml:space="preserve">5743760</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J170">
-        <v>90</v>
+        <v>132</v>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t xml:space="preserve">311594112</t>
+          <t xml:space="preserve">311612678</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
@@ -12749,7 +12749,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-04-21</t>
+          <t xml:space="preserve">2032-07-04</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12791,30 +12791,30 @@
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 166</t>
+          <t xml:space="preserve">Hjertingparken 200</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t xml:space="preserve">5743760</t>
+          <t xml:space="preserve">8388188</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J171">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t xml:space="preserve">311612678</t>
+          <t xml:space="preserve">311623037</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-07-04</t>
+          <t xml:space="preserve">2032-08-25</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12866,40 +12866,40 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hjertingparken 200</t>
+          <t xml:space="preserve">Egedalvej 7C</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388188</t>
+          <t xml:space="preserve">9061836</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J172">
-        <v>130</v>
+        <v>186</v>
       </c>
       <c r="K172" t="inlineStr">
         <is>
-          <t xml:space="preserve">311623037</t>
+          <t xml:space="preserve">311624660</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t xml:space="preserve">VITA Ingeniører</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-08-25</t>
+          <t xml:space="preserve">2032-09-01</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12941,7 +12941,7 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t xml:space="preserve">Egedalvej 7C</t>
+          <t xml:space="preserve">Askekrattet 6</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
@@ -12951,30 +12951,30 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t xml:space="preserve">9061836</t>
+          <t xml:space="preserve">5745656</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J173">
-        <v>186</v>
+        <v>115</v>
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t xml:space="preserve">311624660</t>
+          <t xml:space="preserve">311634690</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">VITA Ingeniører</t>
         </is>
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-09-01</t>
+          <t xml:space="preserve">2032-10-11</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -13016,7 +13016,7 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askekrattet 6</t>
+          <t xml:space="preserve">Askekrattet 8</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
@@ -13031,11 +13031,11 @@
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J174">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="K174" t="inlineStr">
         <is>
@@ -13091,30 +13091,30 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askekrattet 8</t>
+          <t xml:space="preserve">Vester Gjesingvej 30</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">5745656</t>
+          <t xml:space="preserve">5109285</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">5</t>
         </is>
       </c>
       <c r="J175">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="K175" t="inlineStr">
         <is>
-          <t xml:space="preserve">311634690</t>
+          <t xml:space="preserve">311634671</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
@@ -13166,7 +13166,7 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Vester Gjesingvej 30</t>
+          <t xml:space="preserve">Grønlandsparken 300</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
@@ -13176,20 +13176,20 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5109285</t>
+          <t xml:space="preserve">5110960</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J176">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="K176" t="inlineStr">
         <is>
-          <t xml:space="preserve">311634671</t>
+          <t xml:space="preserve">311647854</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
@@ -13199,7 +13199,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-10-11</t>
+          <t xml:space="preserve">2032-12-08</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -13241,40 +13241,40 @@
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønlandsparken 300</t>
+          <t xml:space="preserve">Kvaglundparken 10</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">5110960</t>
+          <t xml:space="preserve">313640</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J177">
-        <v>112</v>
+        <v>228</v>
       </c>
       <c r="K177" t="inlineStr">
         <is>
-          <t xml:space="preserve">311647854</t>
+          <t xml:space="preserve">311653796</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t xml:space="preserve">VITA Ingeniører</t>
+          <t xml:space="preserve">Ankersen ApS</t>
         </is>
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t xml:space="preserve">2032-12-08</t>
+          <t xml:space="preserve">2033-01-12</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kvaglundparken 10</t>
+          <t xml:space="preserve">Grønnegårdsvej 28A</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
@@ -13326,7 +13326,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t xml:space="preserve">313640</t>
+          <t xml:space="preserve">9433154</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -13335,21 +13335,21 @@
         </is>
       </c>
       <c r="J178">
-        <v>228</v>
+        <v>198</v>
       </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t xml:space="preserve">311653796</t>
+          <t xml:space="preserve">311665868</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ankersen ApS</t>
+          <t xml:space="preserve">VITA Ingeniører</t>
         </is>
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-01-12</t>
+          <t xml:space="preserve">2033-03-13</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -13391,7 +13391,7 @@
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 28A</t>
+          <t xml:space="preserve">Grønnegårdsvej 28B</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
@@ -13406,7 +13406,7 @@
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">14</t>
         </is>
       </c>
       <c r="J179">
@@ -13414,7 +13414,7 @@
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665868</t>
+          <t xml:space="preserve">311665870</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -13466,7 +13466,7 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 28B</t>
+          <t xml:space="preserve">Grønnegårdsvej 30A</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
@@ -13481,15 +13481,15 @@
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t xml:space="preserve">14</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J180">
-        <v>198</v>
+        <v>176</v>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665870</t>
+          <t xml:space="preserve">311665854</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -13541,7 +13541,7 @@
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 30A</t>
+          <t xml:space="preserve">Grønnegårdsvej 30B</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
@@ -13556,15 +13556,15 @@
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J181">
-        <v>176</v>
+        <v>209</v>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665854</t>
+          <t xml:space="preserve">311665853</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -13616,30 +13616,30 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 30B</t>
+          <t xml:space="preserve">Nørrebyvej 14</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t xml:space="preserve">9433154</t>
+          <t xml:space="preserve">5050770</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J182">
-        <v>209</v>
+        <v>140</v>
       </c>
       <c r="K182" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665853</t>
+          <t xml:space="preserve">311665859</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
@@ -13691,40 +13691,40 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebyvej 14</t>
+          <t xml:space="preserve">Sorsigvej 10</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t xml:space="preserve">5050770</t>
+          <t xml:space="preserve">5751925</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J183">
-        <v>140</v>
+        <v>75</v>
       </c>
       <c r="K183" t="inlineStr">
         <is>
-          <t xml:space="preserve">311665859</t>
+          <t xml:space="preserve">311672713</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t xml:space="preserve">VITA Ingeniører</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-03-13</t>
+          <t xml:space="preserve">2033-04-11</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13766,40 +13766,40 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sorsigvej 10</t>
+          <t xml:space="preserve">Grønnegårdsvej 8</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t xml:space="preserve">5751925</t>
+          <t xml:space="preserve">5745295</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J184">
-        <v>75</v>
+        <v>90</v>
       </c>
       <c r="K184" t="inlineStr">
         <is>
-          <t xml:space="preserve">311672713</t>
+          <t xml:space="preserve">311683882</t>
         </is>
       </c>
       <c r="L184" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">VITA Ingeniører</t>
         </is>
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-04-11</t>
+          <t xml:space="preserve">2033-05-30</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13841,17 +13841,17 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grønnegårdsvej 8</t>
+          <t xml:space="preserve">Langliparken 7</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t xml:space="preserve">5745295</t>
+          <t xml:space="preserve">5116465</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -13860,11 +13860,11 @@
         </is>
       </c>
       <c r="J185">
-        <v>90</v>
+        <v>185</v>
       </c>
       <c r="K185" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683882</t>
+          <t xml:space="preserve">311683873</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
@@ -13931,11 +13931,11 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J186">
-        <v>185</v>
+        <v>232</v>
       </c>
       <c r="K186" t="inlineStr">
         <is>
@@ -13991,30 +13991,30 @@
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t xml:space="preserve">Langliparken 7</t>
+          <t xml:space="preserve">Nør-Eng 4</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t xml:space="preserve">5116465</t>
+          <t xml:space="preserve">5060108</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
       <c r="J187">
-        <v>232</v>
+        <v>81</v>
       </c>
       <c r="K187" t="inlineStr">
         <is>
-          <t xml:space="preserve">311683873</t>
+          <t xml:space="preserve">311696702</t>
         </is>
       </c>
       <c r="L187" t="inlineStr">
@@ -14024,7 +14024,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-05-30</t>
+          <t xml:space="preserve">2033-07-26</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -14066,7 +14066,7 @@
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nør-Eng 4</t>
+          <t xml:space="preserve">Nør-Eng 6</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
@@ -14081,11 +14081,11 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t xml:space="preserve">7</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J188">
-        <v>81</v>
+        <v>207</v>
       </c>
       <c r="K188" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nør-Eng 6</t>
+          <t xml:space="preserve">Seminarievej 23B</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
@@ -14151,20 +14151,20 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t xml:space="preserve">5060108</t>
+          <t xml:space="preserve">5753446</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J189">
-        <v>207</v>
+        <v>245</v>
       </c>
       <c r="K189" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696702</t>
+          <t xml:space="preserve">311696670</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
@@ -14216,40 +14216,40 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t xml:space="preserve">Seminarievej 23B</t>
+          <t xml:space="preserve">Hovedvej A1 27</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t xml:space="preserve">5753446</t>
+          <t xml:space="preserve">5129039</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J190">
-        <v>245</v>
+        <v>112</v>
       </c>
       <c r="K190" t="inlineStr">
         <is>
-          <t xml:space="preserve">311696670</t>
+          <t xml:space="preserve">311700903</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t xml:space="preserve">VITA Ingeniører</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-07-26</t>
+          <t xml:space="preserve">2033-08-17</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -14291,17 +14291,17 @@
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hovedvej A1 27</t>
+          <t xml:space="preserve">Fridtjof Nansens Vej 45</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t xml:space="preserve">5129039</t>
+          <t xml:space="preserve">5109189</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -14310,11 +14310,11 @@
         </is>
       </c>
       <c r="J191">
-        <v>112</v>
+        <v>211</v>
       </c>
       <c r="K191" t="inlineStr">
         <is>
-          <t xml:space="preserve">311700903</t>
+          <t xml:space="preserve">311748048</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
@@ -14324,7 +14324,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t xml:space="preserve">2033-08-17</t>
+          <t xml:space="preserve">2034-03-26</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -14366,17 +14366,17 @@
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fridtjof Nansens Vej 45</t>
+          <t xml:space="preserve">Ørnevænget 1</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">5109189</t>
+          <t xml:space="preserve">5750798</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -14385,11 +14385,11 @@
         </is>
       </c>
       <c r="J192">
-        <v>211</v>
+        <v>246</v>
       </c>
       <c r="K192" t="inlineStr">
         <is>
-          <t xml:space="preserve">311748048</t>
+          <t xml:space="preserve">311748180</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
@@ -14441,17 +14441,17 @@
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ørnevænget 1</t>
+          <t xml:space="preserve">Topsand 5</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t xml:space="preserve">5750798</t>
+          <t xml:space="preserve">5119158</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -14460,11 +14460,11 @@
         </is>
       </c>
       <c r="J193">
-        <v>246</v>
+        <v>172</v>
       </c>
       <c r="K193" t="inlineStr">
         <is>
-          <t xml:space="preserve">311748180</t>
+          <t xml:space="preserve">311749185</t>
         </is>
       </c>
       <c r="L193" t="inlineStr">
@@ -14474,7 +14474,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-03-26</t>
+          <t xml:space="preserve">2034-04-03</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14516,17 +14516,17 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Topsand 5</t>
+          <t xml:space="preserve">Rolfsgade 63</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">5119158</t>
+          <t xml:space="preserve">5736527</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -14535,21 +14535,21 @@
         </is>
       </c>
       <c r="J194">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="K194" t="inlineStr">
         <is>
-          <t xml:space="preserve">311749185</t>
+          <t xml:space="preserve">311751153</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Energihuset Danmark ApS</t>
         </is>
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-03</t>
+          <t xml:space="preserve">2034-04-11</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14591,7 +14591,7 @@
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolfsgade 63</t>
+          <t xml:space="preserve">Rolfsgade 67</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
@@ -14601,7 +14601,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">5736527</t>
+          <t xml:space="preserve">5736586</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -14610,11 +14610,11 @@
         </is>
       </c>
       <c r="J195">
-        <v>138</v>
+        <v>129</v>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t xml:space="preserve">311751153</t>
+          <t xml:space="preserve">311751314</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -14666,7 +14666,7 @@
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rolfsgade 67</t>
+          <t xml:space="preserve">Bakkevej 6</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
@@ -14676,30 +14676,30 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">5736586</t>
+          <t xml:space="preserve">5747038</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">4</t>
         </is>
       </c>
       <c r="J196">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t xml:space="preserve">311751314</t>
+          <t xml:space="preserve">311757225</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Energihuset Danmark ApS</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-04-11</t>
+          <t xml:space="preserve">2034-05-06</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14741,7 +14741,7 @@
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 6</t>
+          <t xml:space="preserve">Skolebakken 86</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
@@ -14751,20 +14751,20 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">5747038</t>
+          <t xml:space="preserve">5743878</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t xml:space="preserve">4</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J197">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="K197" t="inlineStr">
         <is>
-          <t xml:space="preserve">311757225</t>
+          <t xml:space="preserve">311757226</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
@@ -14816,17 +14816,17 @@
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Skolebakken 86</t>
+          <t xml:space="preserve">Stokbrovej 16</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">5743878</t>
+          <t xml:space="preserve">5123396</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -14835,11 +14835,11 @@
         </is>
       </c>
       <c r="J198">
-        <v>207</v>
+        <v>160</v>
       </c>
       <c r="K198" t="inlineStr">
         <is>
-          <t xml:space="preserve">311757226</t>
+          <t xml:space="preserve">311758142</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
@@ -14849,7 +14849,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-06</t>
+          <t xml:space="preserve">2034-05-08</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14891,30 +14891,30 @@
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stokbrovej 16</t>
+          <t xml:space="preserve">Askekrattet 1</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">5123396</t>
+          <t xml:space="preserve">8274789</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J199">
-        <v>160</v>
+        <v>203</v>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t xml:space="preserve">311758142</t>
+          <t xml:space="preserve">311759421</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -14924,7 +14924,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-08</t>
+          <t xml:space="preserve">2034-05-15</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14966,30 +14966,30 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t xml:space="preserve">Askekrattet 1</t>
+          <t xml:space="preserve">Jupitervænget 57</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t xml:space="preserve">8274789</t>
+          <t xml:space="preserve">5117962</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J200">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="K200" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759421</t>
+          <t xml:space="preserve">311759427</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
@@ -15041,30 +15041,30 @@
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Jupitervænget 57</t>
+          <t xml:space="preserve">Nørrebrogade 102</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">5117962</t>
+          <t xml:space="preserve">5741016</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J201">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="K201" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759427</t>
+          <t xml:space="preserve">311759426</t>
         </is>
       </c>
       <c r="L201" t="inlineStr">
@@ -15116,7 +15116,7 @@
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørrebrogade 102</t>
+          <t xml:space="preserve">Darumvej 110</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
@@ -15126,7 +15126,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">5741016</t>
+          <t xml:space="preserve">7236586</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -15135,11 +15135,11 @@
         </is>
       </c>
       <c r="J202">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="K202" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759426</t>
+          <t xml:space="preserve">311759941</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
@@ -15149,7 +15149,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-15</t>
+          <t xml:space="preserve">2034-05-16</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -15191,40 +15191,40 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Darumvej 110</t>
+          <t xml:space="preserve">Hedelundvej 120</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6705</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t xml:space="preserve">7236586</t>
+          <t xml:space="preserve">5744392</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">6</t>
         </is>
       </c>
       <c r="J203">
-        <v>212</v>
+        <v>103</v>
       </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t xml:space="preserve">311759943</t>
+          <t xml:space="preserve">311775354</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
         </is>
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-05-16</t>
+          <t xml:space="preserve">2034-07-29</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -15266,7 +15266,7 @@
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hedelundvej 120</t>
+          <t xml:space="preserve">John Tranums Vej 38</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t xml:space="preserve">5744392</t>
+          <t xml:space="preserve">7872805</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -15285,21 +15285,21 @@
         </is>
       </c>
       <c r="J204">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t xml:space="preserve">311775354</t>
+          <t xml:space="preserve">311780599</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sweco Danmark A/S - LBF</t>
+          <t xml:space="preserve">Botjek A/S</t>
         </is>
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-07-29</t>
+          <t xml:space="preserve">2034-08-27</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -15341,30 +15341,30 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t xml:space="preserve">John Tranums Vej 38</t>
+          <t xml:space="preserve">Tangevej 6H</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">7872805</t>
+          <t xml:space="preserve">5749171</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t xml:space="preserve">6</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J205">
-        <v>108</v>
+        <v>194</v>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t xml:space="preserve">311780599</t>
+          <t xml:space="preserve">311802433</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
@@ -15374,7 +15374,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-08-27</t>
+          <t xml:space="preserve">2034-12-13</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -15416,40 +15416,40 @@
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tangevej 6H</t>
+          <t xml:space="preserve">Astrupvej 2A</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t xml:space="preserve">5749171</t>
+          <t xml:space="preserve">5108659</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J206">
-        <v>194</v>
+        <v>248</v>
       </c>
       <c r="K206" t="inlineStr">
         <is>
-          <t xml:space="preserve">311802433</t>
+          <t xml:space="preserve">311837308</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t xml:space="preserve">Botjek A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t xml:space="preserve">2034-12-13</t>
+          <t xml:space="preserve">2035-06-11</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -15491,7 +15491,7 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Astrupvej 2A</t>
+          <t xml:space="preserve">Gjesinglund Alle 2</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
@@ -15501,7 +15501,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">5108659</t>
+          <t xml:space="preserve">7395397</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -15510,11 +15510,11 @@
         </is>
       </c>
       <c r="J207">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="K207" t="inlineStr">
         <is>
-          <t xml:space="preserve">311837308</t>
+          <t xml:space="preserve">311847384</t>
         </is>
       </c>
       <c r="L207" t="inlineStr">
@@ -15524,7 +15524,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-06-11</t>
+          <t xml:space="preserve">2035-08-05</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -15581,11 +15581,11 @@
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">3</t>
         </is>
       </c>
       <c r="J208">
-        <v>240</v>
+        <v>124</v>
       </c>
       <c r="K208" t="inlineStr">
         <is>
@@ -15641,40 +15641,40 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gjesinglund Alle 2</t>
+          <t xml:space="preserve">Guldagervej 98</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">7395397</t>
+          <t xml:space="preserve">1492153</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t xml:space="preserve">3</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J209">
-        <v>124</v>
+        <v>237</v>
       </c>
       <c r="K209" t="inlineStr">
         <is>
-          <t xml:space="preserve">311847384</t>
+          <t xml:space="preserve">311853987</t>
         </is>
       </c>
       <c r="L209" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
         </is>
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-08-05</t>
+          <t xml:space="preserve">2035-09-05</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15716,17 +15716,17 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldagervej 98</t>
+          <t xml:space="preserve">Nørremarkvej 29</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6740</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t xml:space="preserve">1492153</t>
+          <t xml:space="preserve">5049304</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -15735,21 +15735,21 @@
         </is>
       </c>
       <c r="J210">
-        <v>237</v>
+        <v>81</v>
       </c>
       <c r="K210" t="inlineStr">
         <is>
-          <t xml:space="preserve">311853987</t>
+          <t xml:space="preserve">311868109</t>
         </is>
       </c>
       <c r="L210" t="inlineStr">
         <is>
-          <t xml:space="preserve">TÜV SÜD Domutech A/S</t>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-09-05</t>
+          <t xml:space="preserve">2035-11-13</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15791,30 +15791,30 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t xml:space="preserve">Nørremarkvej 29</t>
+          <t xml:space="preserve">Ravnsbjergvej 6</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t xml:space="preserve">6740</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t xml:space="preserve">5049304</t>
+          <t xml:space="preserve">8192368</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J211">
-        <v>81</v>
+        <v>249</v>
       </c>
       <c r="K211" t="inlineStr">
         <is>
-          <t xml:space="preserve">311868109</t>
+          <t xml:space="preserve">311870754</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
@@ -15824,7 +15824,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-13</t>
+          <t xml:space="preserve">2035-11-28</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15866,30 +15866,30 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ravnsbjergvej 6</t>
+          <t xml:space="preserve">Tarpgårdsvej 9</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6715</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t xml:space="preserve">8192368</t>
+          <t xml:space="preserve">5111073</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J212">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t xml:space="preserve">311870754</t>
+          <t xml:space="preserve">311871125</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
@@ -15899,7 +15899,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-11-28</t>
+          <t xml:space="preserve">2035-12-01</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15941,17 +15941,17 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tarpgårdsvej 9</t>
+          <t xml:space="preserve">Guldager Stationsvej 105</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t xml:space="preserve">6715</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t xml:space="preserve">5111073</t>
+          <t xml:space="preserve">8388168</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
@@ -15960,11 +15960,11 @@
         </is>
       </c>
       <c r="J213">
-        <v>244</v>
+        <v>168</v>
       </c>
       <c r="K213" t="inlineStr">
         <is>
-          <t xml:space="preserve">311871125</t>
+          <t xml:space="preserve">311874231</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-01</t>
+          <t xml:space="preserve">2035-12-18</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -16031,15 +16031,15 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t xml:space="preserve">1</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J214">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="K214" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874231</t>
+          <t xml:space="preserve">311874233</t>
         </is>
       </c>
       <c r="L214" t="inlineStr">
@@ -16106,11 +16106,11 @@
       </c>
       <c r="I215" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">9</t>
         </is>
       </c>
       <c r="J215">
-        <v>130</v>
+        <v>77</v>
       </c>
       <c r="K215" t="inlineStr">
         <is>
@@ -16166,40 +16166,40 @@
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t xml:space="preserve">Guldager Stationsvej 105</t>
+          <t xml:space="preserve">Kastanie Alle 14</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t xml:space="preserve">6710</t>
+          <t xml:space="preserve">6760</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388168</t>
+          <t xml:space="preserve">8410630</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t xml:space="preserve">9</t>
+          <t xml:space="preserve">13</t>
         </is>
       </c>
       <c r="J216">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311874233</t>
+          <t xml:space="preserve">311916833</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t xml:space="preserve">2035-12-18</t>
+          <t xml:space="preserve">2036-07-28</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -16241,7 +16241,7 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 14</t>
+          <t xml:space="preserve">Kastanie Alle 3A</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
@@ -16256,11 +16256,11 @@
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t xml:space="preserve">13</t>
+          <t xml:space="preserve">21</t>
         </is>
       </c>
       <c r="J217">
-        <v>210</v>
+        <v>126</v>
       </c>
       <c r="K217" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 3A</t>
+          <t xml:space="preserve">Kastanie Alle 6A</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
@@ -16331,11 +16331,11 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t xml:space="preserve">21</t>
+          <t xml:space="preserve">75</t>
         </is>
       </c>
       <c r="J218">
-        <v>126</v>
+        <v>102</v>
       </c>
       <c r="K218" t="inlineStr">
         <is>
@@ -16391,7 +16391,7 @@
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 6A</t>
+          <t xml:space="preserve">Kastanie Alle 6C</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
@@ -16406,7 +16406,7 @@
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t xml:space="preserve">75</t>
+          <t xml:space="preserve">76</t>
         </is>
       </c>
       <c r="J219">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 6C</t>
+          <t xml:space="preserve">Kastanie Alle 6E</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
@@ -16481,11 +16481,11 @@
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t xml:space="preserve">76</t>
+          <t xml:space="preserve">79</t>
         </is>
       </c>
       <c r="J220">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="K220" t="inlineStr">
         <is>
@@ -16541,7 +16541,7 @@
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 6E</t>
+          <t xml:space="preserve">Kastanie Alle 8A</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
@@ -16556,11 +16556,11 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t xml:space="preserve">79</t>
+          <t xml:space="preserve">77</t>
         </is>
       </c>
       <c r="J221">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="K221" t="inlineStr">
         <is>
@@ -16616,7 +16616,7 @@
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 8A</t>
+          <t xml:space="preserve">Kastanie Alle 8C</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
@@ -16631,7 +16631,7 @@
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t xml:space="preserve">77</t>
+          <t xml:space="preserve">78</t>
         </is>
       </c>
       <c r="J222">
@@ -16691,7 +16691,7 @@
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kastanie Alle 8C</t>
+          <t xml:space="preserve">Pile Alle 4</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
@@ -16706,11 +16706,11 @@
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t xml:space="preserve">78</t>
+          <t xml:space="preserve">32</t>
         </is>
       </c>
       <c r="J223">
-        <v>102</v>
+        <v>117</v>
       </c>
       <c r="K223" t="inlineStr">
         <is>
@@ -16766,40 +16766,40 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t xml:space="preserve">Pile Alle 4</t>
+          <t xml:space="preserve">Bakkevej 3</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t xml:space="preserve">6760</t>
+          <t xml:space="preserve">6700</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t xml:space="preserve">8410630</t>
+          <t xml:space="preserve">5747045</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t xml:space="preserve">32</t>
+          <t xml:space="preserve">2</t>
         </is>
       </c>
       <c r="J224">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t xml:space="preserve">311916833</t>
+          <t xml:space="preserve">311919867</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t xml:space="preserve"/>
+          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
         </is>
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-07-28</t>
+          <t xml:space="preserve">2036-08-18</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16841,17 +16841,17 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bakkevej 3</t>
+          <t xml:space="preserve">Plantagevej 35</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t xml:space="preserve">6700</t>
+          <t xml:space="preserve">6710</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">5747045</t>
+          <t xml:space="preserve">7254548</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -16860,11 +16860,11 @@
         </is>
       </c>
       <c r="J225">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919867</t>
+          <t xml:space="preserve">311919928</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t xml:space="preserve">Plantagevej 35</t>
+          <t xml:space="preserve">Krebsens Kvarter 56A</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
@@ -16926,30 +16926,30 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t xml:space="preserve">7254548</t>
+          <t xml:space="preserve">8388213</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2</t>
+          <t xml:space="preserve">8</t>
         </is>
       </c>
       <c r="J226">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="K226" t="inlineStr">
         <is>
-          <t xml:space="preserve">311919928</t>
+          <t xml:space="preserve">311925681</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve">STD Klima og Byggeri ApS</t>
         </is>
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-08-18</t>
+          <t xml:space="preserve">2036-09-14</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16991,7 +16991,7 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t xml:space="preserve">Krebsens Kvarter 56A</t>
+          <t xml:space="preserve">Strynøvej 8</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
@@ -17001,30 +17001,30 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t xml:space="preserve">8388213</t>
+          <t xml:space="preserve">5119870</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t xml:space="preserve">8</t>
+          <t xml:space="preserve">1</t>
         </is>
       </c>
       <c r="J227">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="K227" t="inlineStr">
         <is>
-          <t xml:space="preserve">311925681</t>
+          <t xml:space="preserve">311930444</t>
         </is>
       </c>
       <c r="L227" t="inlineStr">
         <is>
-          <t xml:space="preserve">STD Klima og Byggeri ApS</t>
+          <t xml:space="preserve">NRGi Rådgivning A/S</t>
         </is>
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t xml:space="preserve">2036-09-14</t>
+          <t xml:space="preserve">2036-10-07</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
